--- a/artfynd/A 51214-2022 artfynd.xlsx
+++ b/artfynd/A 51214-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136890230</v>
       </c>
       <c r="B2" t="n">
-        <v>93083</v>
+        <v>93085</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 51214-2022 artfynd.xlsx
+++ b/artfynd/A 51214-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136890230</v>
       </c>
       <c r="B2" t="n">
-        <v>93085</v>
+        <v>93087</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 51214-2022 artfynd.xlsx
+++ b/artfynd/A 51214-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136890230</v>
       </c>
       <c r="B2" t="n">
-        <v>93087</v>
+        <v>93088</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 51214-2022 artfynd.xlsx
+++ b/artfynd/A 51214-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136890230</v>
       </c>
       <c r="B2" t="n">
-        <v>93088</v>
+        <v>93094</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 51214-2022 artfynd.xlsx
+++ b/artfynd/A 51214-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136890230</v>
       </c>
       <c r="B2" t="n">
-        <v>93094</v>
+        <v>93098</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 51214-2022 artfynd.xlsx
+++ b/artfynd/A 51214-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136890230</v>
       </c>
       <c r="B2" t="n">
-        <v>93098</v>
+        <v>93100</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 51214-2022 artfynd.xlsx
+++ b/artfynd/A 51214-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136890230</v>
       </c>
       <c r="B2" t="n">
-        <v>93100</v>
+        <v>93113</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 51214-2022 artfynd.xlsx
+++ b/artfynd/A 51214-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136890230</v>
       </c>
       <c r="B2" t="n">
-        <v>93113</v>
+        <v>93115</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 51214-2022 artfynd.xlsx
+++ b/artfynd/A 51214-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136890230</v>
       </c>
       <c r="B2" t="n">
-        <v>93115</v>
+        <v>93118</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 51214-2022 artfynd.xlsx
+++ b/artfynd/A 51214-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136890230</v>
       </c>
       <c r="B2" t="n">
-        <v>93118</v>
+        <v>93128</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 51214-2022 artfynd.xlsx
+++ b/artfynd/A 51214-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136890230</v>
       </c>
       <c r="B2" t="n">
-        <v>93128</v>
+        <v>93129</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 51214-2022 artfynd.xlsx
+++ b/artfynd/A 51214-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136890230</v>
       </c>
       <c r="B2" t="n">
-        <v>93129</v>
+        <v>93132</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 51214-2022 artfynd.xlsx
+++ b/artfynd/A 51214-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136890230</v>
       </c>
       <c r="B2" t="n">
-        <v>93132</v>
+        <v>93134</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 51214-2022 artfynd.xlsx
+++ b/artfynd/A 51214-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136890230</v>
       </c>
       <c r="B2" t="n">
-        <v>93134</v>
+        <v>93140</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 51214-2022 artfynd.xlsx
+++ b/artfynd/A 51214-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136890230</v>
       </c>
       <c r="B2" t="n">
-        <v>93140</v>
+        <v>93152</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 51214-2022 artfynd.xlsx
+++ b/artfynd/A 51214-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136890230</v>
       </c>
       <c r="B2" t="n">
-        <v>93152</v>
+        <v>93153</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 51214-2022 artfynd.xlsx
+++ b/artfynd/A 51214-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136890230</v>
       </c>
       <c r="B2" t="n">
-        <v>93153</v>
+        <v>93156</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
